--- a/server/xlsx/体系表.xlsx
+++ b/server/xlsx/体系表.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27045" windowHeight="14160" firstSheet="3" activeTab="1"/>
+    <workbookView windowWidth="27045" windowHeight="12060" firstSheet="3" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="sys_称谓_修仙" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="13">
   <si>
     <t>id</t>
   </si>
@@ -65,9 +65,20 @@
 经验值as修为
 物理攻击as物理攻击
 物理防御as体质
-魔法攻击as法术
-魔法防御as精神
+魔法攻击as法术攻击
+魔法防御as法术防御
 技能急速as施法速度</t>
+  </si>
+  <si>
+    <t>火影忍者</t>
+  </si>
+  <si>
+    <t>魔法值as查克拉
+魔法攻击as精神攻击
+魔法防御as精神防御
+物理攻击as体术(攻)
+物理防御as体术(防)
+技能急速as结印速度</t>
   </si>
 </sst>
 </file>
@@ -814,7 +825,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -835,6 +846,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -955,7 +969,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{466436E4-6B78-469E-8548-4450B02446AE}">
+    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{FB7B03AA-0F1A-4A3B-9591-CF377E1559ED}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -1287,10 +1301,10 @@
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1" spans="1:2">
-      <c r="A4" s="8">
+      <c r="A4" s="9">
         <v>1</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="10" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1312,8 +1326,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="3" outlineLevelCol="1"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="1"/>
   <cols>
     <col min="1" max="1" width="18.625" customWidth="1"/>
     <col min="2" max="2" width="33.5" customWidth="1"/>
@@ -1351,6 +1365,14 @@
         <v>10</v>
       </c>
     </row>
+    <row r="5" ht="81" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/server/xlsx/体系表.xlsx
+++ b/server/xlsx/体系表.xlsx
@@ -67,7 +67,8 @@
 物理防御as体质
 魔法攻击as法术攻击
 魔法防御as法术防御
-技能急速as施法速度</t>
+技能急速as施法速度
+魔法恢复as内力恢复</t>
   </si>
   <si>
     <t>火影忍者</t>
@@ -78,7 +79,8 @@
 魔法防御as精神防御
 物理攻击as体术(攻)
 物理防御as体术(防)
-技能急速as结印速度</t>
+技能急速as结印速度
+魔法恢复as查克拉恢复速度</t>
   </si>
 </sst>
 </file>
@@ -825,7 +827,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -846,9 +848,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -969,7 +968,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{FB7B03AA-0F1A-4A3B-9591-CF377E1559ED}">
+    <tableStyle name="黑色浅色系标题行表格样式" count="2" xr9:uid="{81E8DCF6-9445-4735-8745-935118FB1F9E}">
       <tableStyleElement type="wholeTable" dxfId="1"/>
       <tableStyleElement type="headerRow" dxfId="0"/>
     </tableStyle>
@@ -1301,10 +1300,10 @@
       </c>
     </row>
     <row r="4" ht="22.5" customHeight="1" spans="1:2">
-      <c r="A4" s="9">
+      <c r="A4" s="8">
         <v>1</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="9" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1365,11 +1364,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" ht="81" spans="1:2">
+    <row r="5" ht="133" customHeight="1" spans="1:2">
       <c r="A5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>12</v>
       </c>
     </row>
